--- a/ig/DM-AVRIL-2026/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM-AVRIL-2026/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1021,13 +1021,13 @@
     <t>0131</t>
   </si>
   <si>
-    <t>Circulation extracorporelle (CEC) pour assistance circulatoire-respiratoire (ECMO)</t>
+    <t>Circulation extracorporelle (CEC) pour assistance circulatoire/respiratoire (ECMO)</t>
   </si>
   <si>
     <t>0132</t>
   </si>
   <si>
-    <t>Circulation extracorporelle (CEC) pour assistance circulatoire-respiratoire (ECMO) pédiatrique</t>
+    <t>Circulation extracorporelle (CEC) pour assistance circulatoire/respiratoire (ECMO) pédiatrique</t>
   </si>
   <si>
     <t>0133</t>
@@ -3553,7 +3553,7 @@
     <t>0538</t>
   </si>
   <si>
-    <t>Thérapie de groupe ou atelier à médiation orale et-ou écrite (groupe de parole, d'écriture)</t>
+    <t>Thérapie de groupe ou atelier à médiation orale et/ou écrite (groupe de parole, d'écriture)</t>
   </si>
   <si>
     <t>0539</t>
@@ -6514,7 +6514,7 @@
     <t>1014</t>
   </si>
   <si>
-    <t>Fourniture de matériel d'hygiène, de prévention et de RdRD</t>
+    <t>Fourniture de matériel d’hygiène, de prévention et de Réduction des Risques et des Dommages (RdRD)</t>
   </si>
   <si>
     <t>Distribution de matériel de prévention (préservatifs, gel, digues dentaires, documentations, brochures…)</t>
@@ -9622,7 +9622,7 @@
     <t>1453</t>
   </si>
   <si>
-    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
+    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
   </si>
   <si>
     <t>Prévention, évaluation et accompagnement visant à repérer précocement les troubles du développement psychomoteur, du comportement et les Troubles du Neuro-Développement (TND), afin de favoriser le développement harmonieux de l’enfant et son autonomie.</t>
@@ -9907,7 +9907,7 @@
     <t>1498</t>
   </si>
   <si>
-    <t>Accompagnement ergothérapique auprès des proches aidants (proches et professionnels) : apprentissage de techniques d’accompagnement en Accompagnement ergothérapique auprès des proches aidants</t>
+    <t>Accompagnement ergothérapique auprès des proches aidants (proches et professionnels) : apprentissage de techniques d’accompagnement</t>
   </si>
   <si>
     <t>Apprentissage de techniques d’accompagnement ergothérapique qui vise à améliorer la compréhension de l’impact de la pathologie dans le quotidien et à mettre en place des stratégies d’adaptation visant l’amélioration de la qualité de vie et la participation.  Cet accompagnement inclut l’évaluation des compétences, l’orientation professionnelle, la formation, l’adaptation des postes de travail et la coordination avec les acteurs médico-sociaux, afin de favoriser une intégration professionnelle durable et adaptée aux capacités de la personne.Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>
